--- a/excel_model/pricing_roi_model.xlsx
+++ b/excel_model/pricing_roi_model.xlsx
@@ -460,7 +460,7 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2973331923723558</v>
+        <v>0.4377344761380564</v>
       </c>
       <c r="E8">
         <f>B8*(1-C8)*(D8/100)</f>
@@ -492,7 +492,7 @@
         <v>0.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3901599329186062</v>
+        <v>0.4796741891934648</v>
       </c>
       <c r="E9">
         <f>B9*(1-C9)*(D9/100)</f>
@@ -524,7 +524,7 @@
         <v>0.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3438535105503267</v>
+        <v>0.3617929451344151</v>
       </c>
       <c r="E10">
         <f>B10*(1-C10)*(D10/100)</f>
@@ -556,7 +556,7 @@
         <v>0.2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1879726984501805</v>
+        <v>0.5648398143529502</v>
       </c>
       <c r="E11">
         <f>B11*(1-C11)*(D11/100)</f>
@@ -588,7 +588,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.290276780345237</v>
+        <v>0.3196207167100695</v>
       </c>
       <c r="E12">
         <f>B12*(1-C12)*(D12/100)</f>
@@ -620,7 +620,7 @@
         <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.01849231854351047</v>
+        <v>0.1805850142076565</v>
       </c>
       <c r="E13">
         <f>B13*(1-C13)*(D13/100)</f>
@@ -652,7 +652,7 @@
         <v>0.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2767177747298646</v>
+        <v>0.3080511360238043</v>
       </c>
       <c r="E14">
         <f>B14*(1-C14)*(D14/100)</f>
@@ -684,7 +684,7 @@
         <v>0.2</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.03508810019766482</v>
+        <v>-0.2800172861133132</v>
       </c>
       <c r="E15">
         <f>B15*(1-C15)*(D15/100)</f>

--- a/excel_model/pricing_roi_model.xlsx
+++ b/excel_model/pricing_roi_model.xlsx
@@ -460,7 +460,7 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4377344761380564</v>
+        <v>0.2753423799248957</v>
       </c>
       <c r="E8">
         <f>B8*(1-C8)*(D8/100)</f>
@@ -492,7 +492,7 @@
         <v>0.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4796741891934648</v>
+        <v>0.5394154217779193</v>
       </c>
       <c r="E9">
         <f>B9*(1-C9)*(D9/100)</f>
@@ -524,7 +524,7 @@
         <v>0.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3617929451344151</v>
+        <v>0.3162950986484491</v>
       </c>
       <c r="E10">
         <f>B10*(1-C10)*(D10/100)</f>
@@ -556,7 +556,7 @@
         <v>0.2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5648398143529502</v>
+        <v>0.7335583868303382</v>
       </c>
       <c r="E11">
         <f>B11*(1-C11)*(D11/100)</f>
@@ -588,7 +588,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3196207167100695</v>
+        <v>0.2760878693564922</v>
       </c>
       <c r="E12">
         <f>B12*(1-C12)*(D12/100)</f>
@@ -620,7 +620,7 @@
         <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1805850142076565</v>
+        <v>0.1221365940157933</v>
       </c>
       <c r="E13">
         <f>B13*(1-C13)*(D13/100)</f>
@@ -652,7 +652,7 @@
         <v>0.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3080511360238043</v>
+        <v>0.2883270823683442</v>
       </c>
       <c r="E14">
         <f>B14*(1-C14)*(D14/100)</f>
@@ -684,7 +684,7 @@
         <v>0.2</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2800172861133132</v>
+        <v>0.06344571982738402</v>
       </c>
       <c r="E15">
         <f>B15*(1-C15)*(D15/100)</f>

--- a/excel_model/pricing_roi_model.xlsx
+++ b/excel_model/pricing_roi_model.xlsx
@@ -460,7 +460,7 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2753423799248957</v>
+        <v>-0.1584628413025405</v>
       </c>
       <c r="E8">
         <f>B8*(1-C8)*(D8/100)</f>
@@ -492,7 +492,7 @@
         <v>0.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5394154217779193</v>
+        <v>1.243695460423884</v>
       </c>
       <c r="E9">
         <f>B9*(1-C9)*(D9/100)</f>
@@ -524,7 +524,7 @@
         <v>0.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3162950986484491</v>
+        <v>0.2429459458432851</v>
       </c>
       <c r="E10">
         <f>B10*(1-C10)*(D10/100)</f>
@@ -556,7 +556,7 @@
         <v>0.2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7335583868303382</v>
+        <v>2.459355278265559</v>
       </c>
       <c r="E11">
         <f>B11*(1-C11)*(D11/100)</f>
@@ -588,7 +588,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2760878693564922</v>
+        <v>0.3611092477346642</v>
       </c>
       <c r="E12">
         <f>B12*(1-C12)*(D12/100)</f>
@@ -620,7 +620,7 @@
         <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1221365940157933</v>
+        <v>0.110523424811255</v>
       </c>
       <c r="E13">
         <f>B13*(1-C13)*(D13/100)</f>
@@ -652,7 +652,7 @@
         <v>0.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2883270823683442</v>
+        <v>0.3248648295163666</v>
       </c>
       <c r="E14">
         <f>B14*(1-C14)*(D14/100)</f>
@@ -684,7 +684,7 @@
         <v>0.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06344571982738402</v>
+        <v>0.2611602243243956</v>
       </c>
       <c r="E15">
         <f>B15*(1-C15)*(D15/100)</f>

--- a/excel_model/pricing_roi_model.xlsx
+++ b/excel_model/pricing_roi_model.xlsx
@@ -460,7 +460,7 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1584628413025405</v>
+        <v>0.1920012005289267</v>
       </c>
       <c r="E8">
         <f>B8*(1-C8)*(D8/100)</f>
@@ -492,7 +492,7 @@
         <v>0.2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.243695460423884</v>
+        <v>0.6352471713463316</v>
       </c>
       <c r="E9">
         <f>B9*(1-C9)*(D9/100)</f>
@@ -524,7 +524,7 @@
         <v>0.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2429459458432851</v>
+        <v>0.3034779999048036</v>
       </c>
       <c r="E10">
         <f>B10*(1-C10)*(D10/100)</f>
@@ -556,7 +556,7 @@
         <v>0.2</v>
       </c>
       <c r="D11" t="n">
-        <v>2.459355278265559</v>
+        <v>0.7372825028860909</v>
       </c>
       <c r="E11">
         <f>B11*(1-C11)*(D11/100)</f>
@@ -588,7 +588,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3611092477346642</v>
+        <v>0.2976433238520552</v>
       </c>
       <c r="E12">
         <f>B12*(1-C12)*(D12/100)</f>
@@ -620,7 +620,7 @@
         <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.110523424811255</v>
+        <v>0.07669407535956364</v>
       </c>
       <c r="E13">
         <f>B13*(1-C13)*(D13/100)</f>
@@ -652,7 +652,7 @@
         <v>0.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3248648295163666</v>
+        <v>0.4163814108071575</v>
       </c>
       <c r="E14">
         <f>B14*(1-C14)*(D14/100)</f>
@@ -684,7 +684,7 @@
         <v>0.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2611602243243956</v>
+        <v>0.3398438554011794</v>
       </c>
       <c r="E15">
         <f>B15*(1-C15)*(D15/100)</f>

--- a/excel_model/pricing_roi_model.xlsx
+++ b/excel_model/pricing_roi_model.xlsx
@@ -460,7 +460,7 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1920012005289267</v>
+        <v>-0.2124440103788106</v>
       </c>
       <c r="E8">
         <f>B8*(1-C8)*(D8/100)</f>
@@ -492,7 +492,7 @@
         <v>0.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6352471713463316</v>
+        <v>0.8600744363259301</v>
       </c>
       <c r="E9">
         <f>B9*(1-C9)*(D9/100)</f>
@@ -524,7 +524,7 @@
         <v>0.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3034779999048036</v>
+        <v>0.2660316587724256</v>
       </c>
       <c r="E10">
         <f>B10*(1-C10)*(D10/100)</f>
@@ -556,7 +556,7 @@
         <v>0.2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7372825028860909</v>
+        <v>1.477884298366212</v>
       </c>
       <c r="E11">
         <f>B11*(1-C11)*(D11/100)</f>
@@ -588,7 +588,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2976433238520552</v>
+        <v>0.28834603385549</v>
       </c>
       <c r="E12">
         <f>B12*(1-C12)*(D12/100)</f>
@@ -620,7 +620,7 @@
         <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07669407535956364</v>
+        <v>0.05953439531449308</v>
       </c>
       <c r="E13">
         <f>B13*(1-C13)*(D13/100)</f>
@@ -652,7 +652,7 @@
         <v>0.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4163814108071575</v>
+        <v>0.3744327143295638</v>
       </c>
       <c r="E14">
         <f>B14*(1-C14)*(D14/100)</f>
@@ -684,7 +684,7 @@
         <v>0.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3398438554011794</v>
+        <v>0.3902707059577022</v>
       </c>
       <c r="E15">
         <f>B15*(1-C15)*(D15/100)</f>

--- a/excel_model/pricing_roi_model.xlsx
+++ b/excel_model/pricing_roi_model.xlsx
@@ -460,7 +460,7 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2124440103788106</v>
+        <v>-0.2987525565112342</v>
       </c>
       <c r="E8">
         <f>B8*(1-C8)*(D8/100)</f>
@@ -492,7 +492,7 @@
         <v>0.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8600744363259301</v>
+        <v>0.03203828658248922</v>
       </c>
       <c r="E9">
         <f>B9*(1-C9)*(D9/100)</f>
@@ -524,7 +524,7 @@
         <v>0.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2660316587724256</v>
+        <v>0.2620912393948097</v>
       </c>
       <c r="E10">
         <f>B10*(1-C10)*(D10/100)</f>
@@ -556,7 +556,7 @@
         <v>0.2</v>
       </c>
       <c r="D11" t="n">
-        <v>1.477884298366212</v>
+        <v>-0.1936534589221255</v>
       </c>
       <c r="E11">
         <f>B11*(1-C11)*(D11/100)</f>
@@ -588,7 +588,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.28834603385549</v>
+        <v>0.1480171458283686</v>
       </c>
       <c r="E12">
         <f>B12*(1-C12)*(D12/100)</f>
@@ -620,7 +620,7 @@
         <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05953439531449308</v>
+        <v>0.1084271158402677</v>
       </c>
       <c r="E13">
         <f>B13*(1-C13)*(D13/100)</f>
@@ -652,7 +652,7 @@
         <v>0.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3744327143295638</v>
+        <v>0.2688503874917812</v>
       </c>
       <c r="E14">
         <f>B14*(1-C14)*(D14/100)</f>
@@ -684,7 +684,7 @@
         <v>0.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3902707059577022</v>
+        <v>0.3313833281445276</v>
       </c>
       <c r="E15">
         <f>B15*(1-C15)*(D15/100)</f>

--- a/excel_model/pricing_roi_model.xlsx
+++ b/excel_model/pricing_roi_model.xlsx
@@ -460,7 +460,7 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2987525565112342</v>
+        <v>-0.004514839704040504</v>
       </c>
       <c r="E8">
         <f>B8*(1-C8)*(D8/100)</f>
@@ -492,7 +492,7 @@
         <v>0.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03203828658248922</v>
+        <v>0.4908885850676371</v>
       </c>
       <c r="E9">
         <f>B9*(1-C9)*(D9/100)</f>
@@ -524,7 +524,7 @@
         <v>0.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2620912393948097</v>
+        <v>0.2344065315061108</v>
       </c>
       <c r="E10">
         <f>B10*(1-C10)*(D10/100)</f>
@@ -556,7 +556,7 @@
         <v>0.2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1936534589221255</v>
+        <v>0.8508419620279671</v>
       </c>
       <c r="E11">
         <f>B11*(1-C11)*(D11/100)</f>
@@ -588,7 +588,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1480171458283686</v>
+        <v>0.2427971745705372</v>
       </c>
       <c r="E12">
         <f>B12*(1-C12)*(D12/100)</f>
@@ -620,7 +620,7 @@
         <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1084271158402677</v>
+        <v>0.1060040676327117</v>
       </c>
       <c r="E13">
         <f>B13*(1-C13)*(D13/100)</f>
@@ -652,7 +652,7 @@
         <v>0.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2688503874917812</v>
+        <v>0.2255390052511907</v>
       </c>
       <c r="E14">
         <f>B14*(1-C14)*(D14/100)</f>
@@ -684,7 +684,7 @@
         <v>0.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3313833281445276</v>
+        <v>0.1219629441340249</v>
       </c>
       <c r="E15">
         <f>B15*(1-C15)*(D15/100)</f>
